--- a/out/LSTM_Base_repeat_1_000001.xlsx
+++ b/out/LSTM_Base_repeat_1_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003373292045603739</v>
+        <v>-5.756669758725911e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1452440544217792</v>
+        <v>0.02478644151927139</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2908759417944022</v>
+        <v>0.04963924646850443</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5611554224004776</v>
+        <v>0.0957639593566835</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.268313944803885</v>
+        <v>0.2164438953364906</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1726140445941323</v>
+        <v>0.02945753072326762</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.05167725534224</v>
+        <v>0.179473768334904</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03502467366338758</v>
+        <v>0.00597610995085539</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9488419140720368</v>
+        <v>0.1619234161748735</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03033328177829198</v>
+        <v>0.005174115645872323</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.9744446701315259</v>
+        <v>0.1662902512581174</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01482925303698711</v>
+        <v>0.002526964121082358</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9737307672353041</v>
+        <v>0.166164722101992</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007075614562902999</v>
+        <v>0.001203054272881818</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9730351386175699</v>
+        <v>0.1660418645222371</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002945007365912513</v>
+        <v>0.0004982660235487662</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9718407406877153</v>
+        <v>0.1658338437499779</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002039157777079197</v>
+        <v>0.0003437955134918071</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9729721502275802</v>
+        <v>0.1660229282910768</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008486803063552938</v>
+        <v>0.0001406088673481482</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.972627358415768</v>
+        <v>0.1659598438105695</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004373296065529665</v>
+        <v>7.050339205511362e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9726531165020179</v>
+        <v>0.1659601138893289</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000168730012615027</v>
+        <v>2.491725292766325e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9725525829437417</v>
+        <v>0.1659386871990606</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.005712138175756e-05</v>
+        <v>1.103373131740489e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9725632479642923</v>
+        <v>0.1659363773182503</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.186775377162721e-05</v>
+        <v>2.905404250635916e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.972556818856725</v>
+        <v>0.1659311282928672</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.684585023951151e-05</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9725491217071193</v>
+        <v>0.1659256413632066</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.684608918656512e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9725410844492782</v>
+        <v>0.1659200628379036</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-8.659732161629865e-07</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9725350691490402</v>
+        <v>0.1659148693431695</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9725290120673221</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9725231965651687</v>
+        <v>0.1659095415488468</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9725183152669193</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9725133940653715</v>
+        <v>0.1659096212597913</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9725133860942771</v>
+        <v>0.1659096132886969</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9725135455161661</v>
+        <v>0.165909772710586</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.972513800591189</v>
+        <v>0.1659100277856088</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9725135534872605</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9725135136317883</v>
+        <v>0.1659097408262082</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9725135534872605</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.9725136491403943</v>
+        <v>0.1659098763348141</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9725135853716385</v>
+        <v>0.1659098125660582</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.9725135455161661</v>
+        <v>0.165909772710586</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9725132744989546</v>
+        <v>0.1659095016933745</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9725131947880099</v>
+        <v>0.1659094219824297</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9725132426145766</v>
+        <v>0.1659094698089964</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9725133621809937</v>
+        <v>0.1659095893754135</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9725133462388047</v>
+        <v>0.1659095734332246</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.9725133621809937</v>
+        <v>0.1659095893754135</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9725133462388047</v>
+        <v>0.1659095734332246</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.972513402036466</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.972513402036466</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.972513402036466</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.9725135534872605</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9725137687068112</v>
+        <v>0.165909995901231</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9725136810247721</v>
+        <v>0.1659099082191919</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9725136331982054</v>
+        <v>0.1659098603926252</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9725136810247721</v>
+        <v>0.1659099082191919</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9725134976895994</v>
+        <v>0.1659097248840192</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9725135056606938</v>
+        <v>0.1659097328551137</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9725135136317883</v>
+        <v>0.1659097408262082</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9725135614583551</v>
+        <v>0.1659097886527749</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9725136252271109</v>
+        <v>0.1659098524215308</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9725137368224333</v>
+        <v>0.1659099640168531</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.9725137846490001</v>
+        <v>0.1659100118434199</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.9725137447935278</v>
+        <v>0.1659099719879476</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9725136730536776</v>
+        <v>0.1659099002480975</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9725137926200945</v>
+        <v>0.1659100198145143</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9725136331982054</v>
+        <v>0.1659098603926252</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.972513402036466</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9725133542098992</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9725133860942771</v>
+        <v>0.1659096132886969</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9725133701520882</v>
+        <v>0.165909597346508</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9725132505856711</v>
+        <v>0.1659094777800909</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9725132107301988</v>
+        <v>0.1659094379246186</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9725133542098992</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9725134897185049</v>
+        <v>0.1659097169129248</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.972513473776316</v>
+        <v>0.1659097009707359</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9725134100075604</v>
+        <v>0.1659096372019802</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9725133063833324</v>
+        <v>0.1659095335777523</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9725131868169155</v>
+        <v>0.1659094140113352</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9725133063833324</v>
+        <v>0.1659095335777523</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9725133542098992</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9725133302966158</v>
+        <v>0.1659095574910357</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9725133382677102</v>
+        <v>0.1659095654621301</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_1_000001.xlsx
+++ b/out/LSTM_Base_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003373292045603739</v>
+        <v>-0.0002590062467334792</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1452440544217792</v>
+        <v>0.1115204628033765</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2908759417944022</v>
+        <v>0.2233387592077942</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5611554224004776</v>
+        <v>0.430863353147185</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.268313944803885</v>
+        <v>0.9738299754712261</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1726140445941323</v>
+        <v>0.1325354737120365</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.05167725534224</v>
+        <v>0.8074931522635713</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03502467366338758</v>
+        <v>0.02689264006556121</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9488419140720368</v>
+        <v>0.7285345999661162</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03033328177829198</v>
+        <v>0.02328986369516558</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.9744446701315259</v>
+        <v>0.7481926736029783</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01482925303698711</v>
+        <v>0.01138623561801973</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9737307672353041</v>
+        <v>0.747644522825289</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007075614562902999</v>
+        <v>0.005431912399579287</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9730351386175699</v>
+        <v>0.747109242027014</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002945007365912513</v>
+        <v>0.002259697105969448</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9718407406877153</v>
+        <v>0.7461910391354759</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002039157777079197</v>
+        <v>0.001564579810713132</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9729721502275802</v>
+        <v>0.7470586663019948</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008486803063552938</v>
+        <v>0.0006502399030666668</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.972627358415768</v>
+        <v>0.7467927325210018</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004373296065529665</v>
+        <v>0.0003350993500535649</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9726531165020179</v>
+        <v>0.7468113634787663</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000168730012615027</v>
+        <v>0.000128315477958359</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9725525829437417</v>
+        <v>0.7467330203617296</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.005712138175756e-05</v>
+        <v>6.772442418965789e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9725632479642923</v>
+        <v>0.7467400528726934</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.186775377162721e-05</v>
+        <v>3.11389908600499e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.972556818856725</v>
+        <v>0.746733950910232</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.684585023951151e-05</v>
+        <v>1.205041969913093e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9725491217071193</v>
+        <v>0.7467268707032247</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.684608918656512e-06</v>
+        <v>2.378749652309724e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9725410844492782</v>
+        <v>0.7467195566020126</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-8.659732161629865e-07</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9725350691490402</v>
+        <v>0.7467137826230756</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9725290120673221</v>
+        <v>0.7467080134802081</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9725231965651687</v>
+        <v>0.7467024698121056</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9725183152669193</v>
+        <v>0.7466975486583842</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9725133940653715</v>
+        <v>0.7466975885138565</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9725133860942771</v>
+        <v>0.746697580542762</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9725135455161661</v>
+        <v>0.7466977399646512</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.7466976443115177</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.972513800591189</v>
+        <v>0.7466979950396739</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9725135534872605</v>
+        <v>0.7466977479357456</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9725135136317883</v>
+        <v>0.7466977080802734</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.7466976443115177</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.7466977160513678</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.7466976443115177</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9725135534872605</v>
+        <v>0.7466977479357456</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.9725136491403943</v>
+        <v>0.7466978435888794</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9725135853716385</v>
+        <v>0.7466977798201234</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.9725135455161661</v>
+        <v>0.7466977399646512</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.7466977160513678</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9725132744989546</v>
+        <v>0.7466974689474397</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9725131947880099</v>
+        <v>0.7466973892364949</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9725132426145766</v>
+        <v>0.7466974370630617</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9725133621809937</v>
+        <v>0.7466975566294787</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9725133462388047</v>
+        <v>0.7466975406872898</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.9725133621809937</v>
+        <v>0.7466975566294787</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9725133462388047</v>
+        <v>0.7466975406872898</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.972513402036466</v>
+        <v>0.7466975964849509</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.972513402036466</v>
+        <v>0.7466975964849509</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.972513402036466</v>
+        <v>0.7466975964849509</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.9725135534872605</v>
+        <v>0.7466977479357456</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9725137687068112</v>
+        <v>0.7466979631552961</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9725136810247721</v>
+        <v>0.7466978754732572</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9725136331982054</v>
+        <v>0.7466978276466905</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9725136810247721</v>
+        <v>0.7466978754732572</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9725134976895994</v>
+        <v>0.7466976921380845</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9725135056606938</v>
+        <v>0.7466977001091789</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9725135136317883</v>
+        <v>0.7466977080802734</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.7466977160513678</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9725135216028827</v>
+        <v>0.7466977160513678</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9725135614583551</v>
+        <v>0.7466977559068401</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9725136252271109</v>
+        <v>0.746697819675596</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9725137368224333</v>
+        <v>0.7466979312709183</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.9725137846490001</v>
+        <v>0.746697979097485</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.9725137447935278</v>
+        <v>0.7466979392420128</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9725136730536776</v>
+        <v>0.7466978675021627</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9725137926200945</v>
+        <v>0.7466979870685795</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9725136331982054</v>
+        <v>0.7466978276466905</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.972513402036466</v>
+        <v>0.7466975964849509</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9725133542098992</v>
+        <v>0.7466975486583842</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9725133860942771</v>
+        <v>0.746697580542762</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.7466976443115177</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.7466976443115177</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9725133701520882</v>
+        <v>0.7466975646005731</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9725132505856711</v>
+        <v>0.7466974450341561</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9725132107301988</v>
+        <v>0.7466974051786838</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9725133542098992</v>
+        <v>0.7466975486583842</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9725134897185049</v>
+        <v>0.74669768416699</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.972513473776316</v>
+        <v>0.7466976682248011</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.7466976443115177</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9725134100075604</v>
+        <v>0.7466976044560454</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9725133063833324</v>
+        <v>0.7466975008318175</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9725131868169155</v>
+        <v>0.7466973812654004</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9725133063833324</v>
+        <v>0.7466975008318175</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9725133542098992</v>
+        <v>0.7466975486583842</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9725134498630327</v>
+        <v>0.7466976443115177</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9725133302966158</v>
+        <v>0.7466975247451009</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9725133382677102</v>
+        <v>0.7466975327161953</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_1_000001.xlsx
+++ b/out/LSTM_Base_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02014636248350143</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01211410015821457</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007648445665836334</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.005939999595284462</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.004002459347248077</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001156577840447426</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003067100420594215</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003421014174818993</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001094194129109383</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001442750915884972</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0006392467767000198</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.000991232693195343</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0009278189390897751</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004588734358549118</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.006871627643704414</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.007055515423417091</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002855697646737099</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001188773661851883</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.946808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0006966274231672287</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0006984584033489227</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.00153668038547039</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001225057989358902</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0008948557078838348</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0001601353287696838</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001585425809025764</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.002500128000974655</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.002693952992558479</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.003051964566111565</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0009728781878948212</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.00206870399415493</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001005573198199272</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002137383446097374</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.003811540082097054</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3557798495655082</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.003539206460118294</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.00276021845638752</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0005587693303823471</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001641502603888512</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.179279226522314</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0035419762134552</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.008775589987635612</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01281879283487797</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01851275004446507</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02111812122166157</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002590062467334792</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1115204628033765</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02705503813922405</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2233387592077942</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.430863353147185</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02615928836166859</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.946808764566225</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9738299754712261</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1325354737120365</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.003667613491415977</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8074931522635713</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02689264006556121</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.008951099589467049</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7285345999661162</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02328986369516558</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01971940696239471</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.7481926736029783</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01138623561801973</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01724532432854176</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.747644522825289</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005431912399579287</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01482735760509968</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.747109242027014</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002259697105969448</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01201129704713821</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7461910391354759</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001564579810713132</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01062089577317238</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7470586663019948</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006502399030666668</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.005354265682399273</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7467927325210018</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003350993500535649</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.004422919824719429</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7468113634787663</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000128315477958359</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.009637417271733284</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7467330203617296</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.772442418965789e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01072577759623528</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7467400528726934</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.11389908600499e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01216079108417034</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.746733950910232</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.205041969913093e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.009889757260680199</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7467268707032247</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.378749652309724e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.007749954238533974</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7467195566020126</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.69277857293039e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.006087242625653744</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7467137826230756</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.005272092297673225</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7467080134802081</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.00551227293908596</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7467024698121056</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003271149471402168</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7466975486583842</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00441422127187252</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7466975885138565</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001323429867625237</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.746697580542762</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001708785071969032</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7466977399646512</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.002456948161125183</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.179279226522314</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7466976443115177</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0005098637193441391</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.179279226522314</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7466979950396739</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.004493067041039467</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7466977479357456</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.00526302307844162</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3557798495655082</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7466977080802734</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00737579632550478</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7466976443115177</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.006984693929553032</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7466977160513678</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.006151239387691021</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7466976443115177</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.007486382499337196</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7466977479357456</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.002746064215898514</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.179279226522314</v>
+        <v>0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7466978435888794</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.00661432184278965</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7466977798201234</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01117734331637621</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7466977399646512</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.009433288127183914</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7466977160513678</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.009838368743658066</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7466974689474397</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.009424156509339809</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7466973892364949</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006748432293534279</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7466974370630617</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004980297759175301</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7466975566294787</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002193531021475792</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7466975406872898</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.001417873427271843</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7466975566294787</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.0003974419087171555</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7466975406872898</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0007799975574016571</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7466975964849509</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002472341060638428</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7466975964849509</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.00222834013402462</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7466975964849509</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0002600960433483124</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7466977479357456</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.004276221618056297</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.179279226522314</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7466979631552961</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.00126752071082592</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7466978754732572</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.00338355265557766</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3557798495655082</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7466978276466905</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003917912021279335</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7466978754732572</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.005921473726630211</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7466976921380845</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.006016897037625313</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7466977001091789</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003511602059006691</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7466977080802734</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003763409331440926</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7466977160513678</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003126870840787888</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2117496884784028</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7466977160513678</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.001784812659025192</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.179279226522314</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7466977559068401</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001909801736474037</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.746697819675596</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.001530341804027557</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.179279226522314</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7466979312709183</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.002076549455523491</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.746697979097485</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003020377829670906</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7466979392420128</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.00227014534175396</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7466978675021627</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002887969836592674</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7466979870685795</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003966663032770157</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7466978276466905</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.007578305900096893</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7466975964849509</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.008377762511372566</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7466975486583842</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.007859266363084316</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.746697580542762</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004891186952590942</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7466976443115177</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.00487926509231329</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7466976443115177</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004683183506131172</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7466975646005731</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004437882453203201</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7466974450341561</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003124712035059929</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7466974051786838</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.0005661752074956894</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7466975486583842</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>4.331953823566437e-05</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.74669768416699</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001527609303593636</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7466976682248011</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.001813635230064392</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7466976443115177</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002157200127840042</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7466976044560454</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002073014155030251</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7466975008318175</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0003225803375244141</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7466973812654004</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002426056191325188</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7466975008318175</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001487022265791893</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7466975486583842</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.00287003256380558</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7466976443115177</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002922443673014641</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7466975247451009</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0007856637239456177</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7466975327161953</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_1_000001.xlsx
+++ b/out/LSTM_Base_repeat_1_000001.xlsx
@@ -51029,7 +51029,7 @@
         <v>-0.003271149471402168</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0.523735623362795</v>
@@ -51824,7 +51824,7 @@
         <v>-0.00441422127187252</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0.5237356632182673</v>
@@ -52619,7 +52619,7 @@
         <v>-0.001323429867625237</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC65" t="n">
         <v>0.5237356552471728</v>
@@ -53414,7 +53414,7 @@
         <v>-0.001708785071969032</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0.5237358146690619</v>
@@ -54209,7 +54209,7 @@
         <v>0.002456948161125183</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0.5237357190159284</v>
@@ -55004,7 +55004,7 @@
         <v>0.0005098637193441391</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>0.5237360697440847</v>
@@ -56594,7 +56594,7 @@
         <v>-0.00526302307844162</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0.5237357827846841</v>
